--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4305,7 +4305,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>157</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>74</v>
@@ -4709,7 +4709,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>166</v>
       </c>
@@ -4724,13 +4724,13 @@
         <v>62</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4812,7 +4812,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>169</v>
       </c>
@@ -4827,13 +4827,13 @@
         <v>170</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -5121,7 +5121,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>181</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4923" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4923" uniqueCount="444">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -747,6 +747,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Organizer.code.qualifier</t>
@@ -6543,7 +6547,7 @@
         <v>74</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>74</v>
@@ -6551,17 +6555,17 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>80</v>
@@ -6579,11 +6583,11 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6634,7 +6638,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6654,17 +6658,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
@@ -6685,10 +6689,10 @@
         <v>160</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6739,7 +6743,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6759,10 +6763,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6838,7 +6842,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6858,10 +6862,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6887,10 +6891,10 @@
         <v>91</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6921,7 +6925,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>74</v>
@@ -6939,7 +6943,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -6959,10 +6963,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6985,13 +6989,13 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7042,7 +7046,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7062,10 +7066,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7088,13 +7092,13 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7145,7 +7149,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7165,10 +7169,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7191,7 +7195,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -7244,7 +7248,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7264,10 +7268,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7290,13 +7294,13 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7347,7 +7351,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7367,10 +7371,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7393,10 +7397,10 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
@@ -7448,7 +7452,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7468,10 +7472,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7494,7 +7498,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -7547,7 +7551,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7567,10 +7571,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7593,13 +7597,13 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7650,7 +7654,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7670,10 +7674,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7696,7 +7700,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7749,7 +7753,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7769,10 +7773,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7795,7 +7799,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7848,7 +7852,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7868,10 +7872,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7894,7 +7898,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7947,7 +7951,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7967,10 +7971,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7993,7 +7997,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -8034,7 +8038,7 @@
         <v>74</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
@@ -8044,7 +8048,7 @@
         <v>124</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8064,13 +8068,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>74</v>
@@ -8092,10 +8096,10 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
@@ -8147,7 +8151,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -8167,10 +8171,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8268,10 +8272,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8369,10 +8373,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8470,10 +8474,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8571,10 +8575,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8674,10 +8678,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8777,10 +8781,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8880,10 +8884,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8983,10 +8987,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9084,10 +9088,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9117,14 +9121,14 @@
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>74</v>
@@ -9143,7 +9147,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -9161,7 +9165,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9181,10 +9185,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9218,7 +9222,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>74</v>
@@ -9260,7 +9264,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9280,10 +9284,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9306,7 +9310,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9359,7 +9363,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9379,10 +9383,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9405,7 +9409,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9458,7 +9462,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9478,10 +9482,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9504,7 +9508,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9557,7 +9561,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9577,10 +9581,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9603,7 +9607,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9656,7 +9660,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9676,10 +9680,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9702,7 +9706,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9755,7 +9759,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9775,10 +9779,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9801,7 +9805,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9854,7 +9858,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9874,10 +9878,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9900,7 +9904,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9953,7 +9957,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9973,10 +9977,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9999,7 +10003,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -10052,7 +10056,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -10072,10 +10076,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10098,7 +10102,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -10151,7 +10155,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10171,10 +10175,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10197,7 +10201,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10250,7 +10254,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10270,10 +10274,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10296,7 +10300,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10349,7 +10353,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10369,10 +10373,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10395,7 +10399,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10448,7 +10452,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10468,13 +10472,13 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>74</v>
@@ -10496,10 +10500,10 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
@@ -10551,7 +10555,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10571,10 +10575,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10672,10 +10676,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10773,10 +10777,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10874,10 +10878,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10975,10 +10979,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11078,10 +11082,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11181,10 +11185,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11284,10 +11288,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11387,10 +11391,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11488,10 +11492,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11521,14 +11525,14 @@
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>74</v>
@@ -11547,7 +11551,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>74</v>
@@ -11565,7 +11569,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11585,10 +11589,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11622,7 +11626,7 @@
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>74</v>
@@ -11664,7 +11668,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11684,10 +11688,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11710,7 +11714,7 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -11763,7 +11767,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11783,10 +11787,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11809,7 +11813,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -11862,7 +11866,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11882,10 +11886,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11908,7 +11912,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -11961,7 +11965,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11981,10 +11985,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12007,7 +12011,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -12060,7 +12064,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -12080,10 +12084,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12106,7 +12110,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12159,7 +12163,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12179,10 +12183,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12205,7 +12209,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12258,7 +12262,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12278,10 +12282,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12304,7 +12308,7 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12357,7 +12361,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12377,10 +12381,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12403,7 +12407,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12456,7 +12460,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12476,10 +12480,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12502,7 +12506,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12555,7 +12559,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12575,10 +12579,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12601,7 +12605,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12654,7 +12658,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12674,10 +12678,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12700,7 +12704,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12753,7 +12757,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12773,10 +12777,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12799,7 +12803,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12852,7 +12856,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12872,13 +12876,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>74</v>
@@ -12900,10 +12904,10 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
@@ -12955,7 +12959,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12975,10 +12979,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13076,10 +13080,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13177,10 +13181,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13278,10 +13282,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13379,10 +13383,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13482,10 +13486,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13585,10 +13589,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13688,10 +13692,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13791,10 +13795,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13892,10 +13896,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13925,14 +13929,14 @@
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>74</v>
@@ -13951,7 +13955,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>74</v>
@@ -13969,7 +13973,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -13989,10 +13993,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14026,7 +14030,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>74</v>
@@ -14068,7 +14072,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14088,10 +14092,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14114,7 +14118,7 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
@@ -14167,7 +14171,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14187,10 +14191,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14213,7 +14217,7 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -14266,7 +14270,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14286,10 +14290,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14312,7 +14316,7 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -14365,7 +14369,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14385,10 +14389,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14411,7 +14415,7 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -14464,7 +14468,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14484,10 +14488,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14510,7 +14514,7 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -14563,7 +14567,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14583,10 +14587,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14609,7 +14613,7 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -14662,7 +14666,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14682,10 +14686,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14708,7 +14712,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14761,7 +14765,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14781,10 +14785,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14807,7 +14811,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -14860,7 +14864,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -14880,10 +14884,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14906,7 +14910,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -14959,7 +14963,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -14979,10 +14983,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15005,7 +15009,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -15058,7 +15062,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15078,10 +15082,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15104,7 +15108,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15157,7 +15161,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15177,10 +15181,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15203,7 +15207,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15256,7 +15260,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15276,13 +15280,13 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>74</v>
@@ -15304,10 +15308,10 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
@@ -15359,7 +15363,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15379,10 +15383,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15480,10 +15484,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15581,10 +15585,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15682,10 +15686,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15783,10 +15787,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15886,10 +15890,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -15989,10 +15993,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16092,10 +16096,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16195,10 +16199,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16296,10 +16300,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16329,14 +16333,14 @@
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>74</v>
@@ -16355,7 +16359,7 @@
       </c>
       <c r="Y145" s="2"/>
       <c r="Z145" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>74</v>
@@ -16373,7 +16377,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16393,10 +16397,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16430,7 +16434,7 @@
       </c>
       <c r="Q146" s="2"/>
       <c r="R146" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="S146" t="s" s="2">
         <v>74</v>
@@ -16472,7 +16476,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -16492,10 +16496,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16518,7 +16522,7 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
@@ -16571,7 +16575,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -16591,10 +16595,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16617,7 +16621,7 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
@@ -16670,7 +16674,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -16690,10 +16694,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16716,7 +16720,7 @@
         <v>74</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
@@ -16769,7 +16773,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -16789,10 +16793,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16815,7 +16819,7 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
@@ -16868,7 +16872,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -16888,10 +16892,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -16914,7 +16918,7 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
@@ -16967,7 +16971,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -16987,10 +16991,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17013,7 +17017,7 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
@@ -17066,7 +17070,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17086,10 +17090,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17112,7 +17116,7 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
@@ -17165,7 +17169,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17185,10 +17189,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17211,7 +17215,7 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -17264,7 +17268,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -17284,10 +17288,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17310,7 +17314,7 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -17363,7 +17367,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -17383,10 +17387,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17409,7 +17413,7 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
@@ -17462,7 +17466,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -17482,10 +17486,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17508,7 +17512,7 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -17561,7 +17565,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -17581,10 +17585,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17607,7 +17611,7 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -17660,7 +17664,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
